--- a/ipo-analysis/companies/maxwell-engineering-solutions-ltd/MAXWELL_ENGINEERING_SOLU_03_Valuation.xlsx
+++ b/ipo-analysis/companies/maxwell-engineering-solutions-ltd/MAXWELL_ENGINEERING_SOLU_03_Valuation.xlsx
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>30.76</v>
+        <v>29.45</v>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
